--- a/backend/output_db/final_timetable.xlsx
+++ b/backend/output_db/final_timetable.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,49 +431,49 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Slot 1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Slot 2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Slot 3</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Slot 5</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Slot 6</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Slot 7</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Slot 8</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
@@ -513,7 +525,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
@@ -565,7 +577,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
@@ -607,7 +619,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -659,7 +671,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
@@ -720,49 +732,49 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Slot 1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Slot 2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Slot 3</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Slot 5</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Slot 6</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Slot 7</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Slot 8</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
@@ -820,7 +832,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
@@ -924,7 +936,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -977,7 +989,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
@@ -1043,49 +1055,49 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Slot 1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Slot 2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Slot 3</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Slot 5</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Slot 6</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Slot 7</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Slot 8</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
@@ -1130,7 +1142,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
@@ -1177,7 +1189,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
@@ -1224,7 +1236,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
@@ -1274,7 +1286,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>

--- a/backend/output_db/final_timetable.xlsx
+++ b/backend/output_db/final_timetable.xlsx
@@ -10,6 +10,7 @@
     <sheet name="SY Timetable" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="TY Timetable" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="LY Timetable" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="UNKNOWN Timetable" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1333,4 +1334,370 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Slot 1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Slot 2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Slot 3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Slot 5</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Slot 6</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Slot 7</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Slot 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CS (THEO) - PV |
+CCS (THEO) - TD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MWE (PRAC) - KR |
+BCE (PRAC) - PP |
+SBL-III (PRAC) - RAK |
+CCS (PRAC) - TD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MWE (PRAC) - KR |
+BCE (PRAC) - PP |
+AIML (THEO) - PRH |
+SBL-III (PRAC) - RAK |
+DVD (THEO) - SVM |
+CCS (PRAC) - TD</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BDA (THEO) - AK |
+DCE (PRAC) - JK |
+CCS (PRAC) - PH</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DCE (PRAC) - JK |
+MEW (THEO) - KR |
+CCS (PRAC) - PH |
+DVD (PRAC) - SVM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CS (PRAC) - PV |
+DVD (PRAC) - SVM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CS (PRAC) - PV |
+CCS (THEO) - TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DVD (PRAC) - SVM |
+CCS (THEO) - TD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BCE (PRAC) - PP |
+SBL-III (PRAC) - RAK |
+DVD (PRAC) - SS |
+DVD (PRAC) - SVM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BCE (PRAC) - PP |
+SBL-III (PRAC) - RAK |
+DVD (PRAC) - SS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MEW (THEO) - KR</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>BDA (THEO) - AK |
+MEW (THEO) - KR |
+BCE(A) (THEO) - PP |
+SBL+PBL (PRAC) - RAK |
+DVD (THEO) - SVM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BCE (THEO) - AP |
+DCE (THEO) - JK |
+AIML (PRAC) - PRH |
+SBL+PBL (PRAC) - RAK |
+DVD (PRAC) - SS |
+DVD (THEO) - SVM |
+CCS (PRAC) - TD</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AIML (PRAC) - PRH |
+DVD (PRAC) - SS |
+CCS (PRAC) - TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BCE (THEO) - AP |
+MWE (PRAC) - KR |
+AIML (THEO) - PRH |
+ESR (THEO) - SS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MWE (PRAC) - KR |
+BCE (PRAC) - PP |
+CCS (PRAC) - PRH |
+CS (PRAC) - PV |
+SBL-III (PRAC) - RAK |
+SBL - VII (THEO) - RK |
+CCS (THEO) - TD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BCE (PRAC) - PP |
+CCS (PRAC) - PRH |
+CS (PRAC) - PV |
+SBL-III (PRAC) - RAK |
+DVD (THEO) - SVM</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BDA (PRAC) - AK |
+BCE (PRAC) - AP |
+AIML (PRAC) - PRH</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BDA (PRAC) - AK |
+BCE (PRAC) - AP |
+AIML (PRAC) - PRH |
+TBL+PBL (PRAC) - RAK |
+DVD (PRAC) - SS</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BDA (PRAC) - AK |
+DCE (THEO) - JK |
+MEW (THEO) - KR |
+AIML (THEO) - PRH |
+TBL+PBL (PRAC) - RAK |
+DVD (PRAC) - SS |
+DVD (PRAC) - SVM |
+CCS (THEO) - TD</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>BDA (PRAC) - AK |
+DVD (PRAC) - SVM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CCS (PRAC) - TD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DCE (THEO) - JK |
+AIML (PRAC) - PRH |
+SBL - VII (THEO) - RA |
+SBL-III (PRAC) - RAK |
+CCS (PRAC) - TD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MEW (THEO) - KR |
+AIML (PRAC) - PRH |
+SBL-III (PRAC) - RAK</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MWE (PRAC) - KR |
+BCE (PRAC) - PP |
+AIML (THEO) - PRH |
+DVD (THEO) - SVM</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BCE (PRAC) - AP |
+MWE (PRAC) - KR |
+BCE (PRAC) - PP |
+AIML (PRAC) - PRH</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BCE (PRAC) - AP |
+AIML (PRAC) - PRH |
+SBL-III (PRAC) - RAK |
+SBL - VII (THEO) - RK</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CS (THEO) - PV |
+SBL-III (PRAC) - RAK |
+ESR (THEO) - SS |
+DVD (THEO) - SVM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BDA (THEO) - AK |
+MWE (PRAC) - KR |
+BCE(A) (THEO) - PP |
+CS (THEO) - PV |
+SBL-III (PRAC) - RAK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MWE (PRAC) - KR |
+SBL - VII (THEO) - RA |
+SBL-III (PRAC) - RAK |
+ESR (PRAC) - SS |
+CCS (PRAC) - TD |
+BCE (PRAC) - VD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MEW (THEO) - KR |
+ESR (PRAC) - SS |
+CCS (PRAC) - TD |
+BCE (PRAC) - VD</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DVD (PRAC) - SS |
+CCS (THEO) - TD</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BCE (PRAC) - AP |
+DVD (PRAC) - SS |
+DVD (PRAC) - SVM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>BDA (PRAC) - AK |
+BCE (PRAC) - AP |
+CCS (PRAC) - RAK |
+DVD (PRAC) - SVM</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>BDA (PRAC) - AK |
+CS (THEO) - PV |
+CCS (PRAC) - RAK |
+ESR (THEO) - SS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>